--- a/Tool/MyExcelTool/Excel/language/lang_system.xlsx
+++ b/Tool/MyExcelTool/Excel/language/lang_system.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>结束游戏</t>
+  </si>
+  <si>
+    <t>{0}/{1}</t>
   </si>
 </sst>
 </file>
@@ -1029,8 +1032,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="19.6333333333333" customWidth="1"/>
     <col min="2" max="2" width="37.2583333333333" customWidth="1"/>
@@ -1122,6 +1125,32 @@
       </c>
       <c r="C8">
         <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>910005</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10">
+        <v>910006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11">
+        <v>910007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12">
+        <v>910008</v>
       </c>
     </row>
   </sheetData>
